--- a/data/trans_orig/KIDMED_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>76005</t>
+          <t>76942</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67178</t>
+          <t>68812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>83340</t>
+          <t>84991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>81297</t>
+          <t>82982</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61656</t>
+          <t>62707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94225</t>
+          <t>97607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>157301</t>
+          <t>159924</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135844</t>
+          <t>135241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174463</t>
+          <t>174962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37519</t>
+          <t>36582</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>28773</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54667</t>
+          <t>52982</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74483</t>
+          <t>73438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>107</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>92186</t>
+          <t>89564</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>73892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114661</t>
+          <t>114491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111841</t>
+          <t>111818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137650</t>
+          <t>137742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,82 +1201,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>231</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>169756</t>
+          <t>170934</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151759</t>
+          <t>154410</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184174</t>
+          <t>184135</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>419</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>296614</t>
+          <t>297791</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>273492</t>
+          <t>277319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>316087</t>
+          <t>316011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47036</t>
+          <t>47193</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72797</t>
+          <t>73229</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,82 +1314,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73380</t>
+          <t>72203</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58411</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90367</t>
+          <t>87876</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>165</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>131309</t>
+          <t>130131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>112458</t>
+          <t>111982</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>153831</t>
+          <t>151614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1632,107 +1632,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85468</t>
+          <t>85884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53794</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105327</t>
+          <t>106437</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>92412</t>
+          <t>93457</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78080</t>
+          <t>80527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106743</t>
+          <t>107744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>177881</t>
+          <t>179342</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>143094</t>
+          <t>136948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>201807</t>
+          <t>204660</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -1745,107 +1745,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97356</t>
+          <t>96940</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76934</t>
+          <t>76292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132080</t>
+          <t>130836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78024</t>
+          <t>76979</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64913</t>
+          <t>63568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91624</t>
+          <t>90226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>188</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>175381</t>
+          <t>173920</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151040</t>
+          <t>148729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212579</t>
+          <t>222263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28039</t>
+          <t>28059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2088,107 +2088,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>148</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>102732</t>
+          <t>104330</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92007</t>
+          <t>93621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113111</t>
+          <t>114800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>117772</t>
+          <t>118743</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106181</t>
+          <t>106447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127436</t>
+          <t>129310</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>305</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>220503</t>
+          <t>223073</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>204179</t>
+          <t>206819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>235490</t>
+          <t>237053</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,35%</t>
         </is>
       </c>
     </row>
@@ -2201,107 +2201,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52714</t>
+          <t>51115</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43328</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63124</t>
+          <t>61292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52894</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43374</t>
+          <t>41895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63677</t>
+          <t>63433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>143</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>105608</t>
+          <t>103039</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>91142</t>
+          <t>88187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120546</t>
+          <t>117825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25127</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -2544,107 +2544,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>585</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>391062</t>
+          <t>394014</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>338588</t>
+          <t>342979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>418124</t>
+          <t>421661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>613</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>461237</t>
+          <t>466116</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>428847</t>
+          <t>435981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>487817</t>
+          <t>495052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>852300</t>
+          <t>860130</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>787861</t>
+          <t>796725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>891020</t>
+          <t>899449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -2657,107 +2657,107 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>306</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>245518</t>
+          <t>242566</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>219739</t>
+          <t>214177</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>302666</t>
+          <t>294628</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>258966</t>
+          <t>254087</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>232911</t>
+          <t>224987</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>290726</t>
+          <t>285754</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>603</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>504483</t>
+          <t>496653</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>466861</t>
+          <t>457445</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>573183</t>
+          <t>565634</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24120</t>
+          <t>24904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16643</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35530</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56070</t>
+          <t>54260</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KIDMED_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escala de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
+          <t>Menores según tipo de adherencia a la dieta mediterránea (Kidmed) en 2023 (tasa de respuesta: 96,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79579</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61039</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89955</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>49,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>76942</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>68812</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>84991</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>67,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>79987</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62707</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97607</t>
+          <t>88571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>159924</t>
+          <t>159565</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135241</t>
+          <t>138693</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174962</t>
+          <t>172158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42676</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32209</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61630</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>36582</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28773</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44793</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52982</t>
+          <t>37856</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>29683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73438</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>89564</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73892</t>
+          <t>68127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114491</t>
+          <t>100589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,92 +961,92 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3828</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3766</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4673</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1578</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>5012</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>163958</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>148753</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>175598</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>126857</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>111818</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>137742</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>68,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,01%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>170934</t>
+          <t>128224</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154410</t>
+          <t>118211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184135</t>
+          <t>139238</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>297791</t>
+          <t>292181</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277319</t>
+          <t>273836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>316011</t>
+          <t>307599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>63576</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>51999</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>78331</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>27,49%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>57928</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>47193</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>73229</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>25,36%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>39,35%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72203</t>
+          <t>51135</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>87876</t>
+          <t>60838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>130131</t>
+          <t>114712</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111982</t>
+          <t>98849</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>151614</t>
+          <t>132326</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7483</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3632</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>84763</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>72034</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>97109</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>50,9%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>43,26%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>85884</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>52389</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>106437</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,83%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>56,54%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>93457</t>
+          <t>82092</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80527</t>
+          <t>71648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>107744</t>
+          <t>92601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>179342</t>
+          <t>166856</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>136948</t>
+          <t>151018</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>204660</t>
+          <t>186180</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>70078</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58267</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83455</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>50,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>96940</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>76292</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>130836</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>51,5%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>40,53%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>69,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76979</t>
+          <t>67191</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63568</t>
+          <t>56451</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90226</t>
+          <t>77673</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>173920</t>
+          <t>137269</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>148729</t>
+          <t>118204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222263</t>
+          <t>152918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11681</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18886</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5424</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2227</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10466</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>110722</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>99750</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>120854</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>104330</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>93621</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>114800</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,78%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>118743</t>
+          <t>103337</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106447</t>
+          <t>92638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129310</t>
+          <t>113510</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>223073</t>
+          <t>214059</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206819</t>
+          <t>198552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>237053</t>
+          <t>228668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>49100</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>39427</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>59372</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>51115</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>41127</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>61292</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>31,07%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51923</t>
+          <t>51137</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41895</t>
+          <t>41361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63433</t>
+          <t>61366</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>103039</t>
+          <t>100238</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88187</t>
+          <t>86835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117825</t>
+          <t>115592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6342</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2517</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>9074</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4723</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14941</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>439023</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>411473</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>463185</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>585</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>394014</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>342979</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>421661</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>435981</t>
+          <t>374528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>495052</t>
+          <t>412911</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>796725</t>
+          <t>798965</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>899449</t>
+          <t>863679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>225430</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>201867</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>254502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>32,82%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>37,05%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>242566</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>214177</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>294628</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>45,11%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>254087</t>
+          <t>207320</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>224987</t>
+          <t>189683</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>285754</t>
+          <t>227608</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>496653</t>
+          <t>432750</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>457445</t>
+          <t>403133</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>565634</t>
+          <t>466004</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14389</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>31658</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>24904</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
